--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -663,31 +663,31 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
-        <v>35</v>
-      </c>
       <c r="M5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -939,10 +939,10 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|6|10|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1191,31 +1191,31 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1282,19 +1282,19 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|14|17|25|35</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1458,28 +1458,28 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>35</v>
-      </c>
       <c r="M12" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|13|25|35</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.94</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -675,19 +675,19 @@
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.94</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="n">
         <v>25</v>
       </c>
-      <c r="L4" t="n">
-        <v>35</v>
-      </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.94</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>40.44</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -927,31 +927,31 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>38.94</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>37.94</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.22571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>36.69</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.27333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1370,19 +1370,19 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.94</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1464,13 +1464,13 @@
         <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.66727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.94</v>
+        <v>73.72</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" t="n">
         <v>25</v>
       </c>
-      <c r="L3" t="n">
-        <v>33</v>
-      </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.94</v>
+        <v>47.72</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
         <v>21</v>
@@ -766,7 +766,7 @@
         <v>25</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.94</v>
+        <v>42.72</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.44</v>
+        <v>40.22</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -927,13 +927,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.94</v>
+        <v>38.72</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1015,31 +1015,31 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.94</v>
+        <v>37.72</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.22571428571428</v>
+        <v>37.00571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1191,31 +1191,31 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>74</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
-      <c r="M9" t="n">
-        <v>73</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.27333333333333</v>
+        <v>36.05333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|10|11|25|33</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.94</v>
+        <v>35.72</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>7|10|12|23|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.66727272727273</v>
+        <v>35.44727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|6|9|22|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.72</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.72</v>
+        <v>47.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.72</v>
+        <v>42.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -842,19 +842,19 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.22</v>
+        <v>40.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -927,13 +927,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.72</v>
+        <v>38.9</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1015,31 +1015,31 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.72</v>
+        <v>37.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1103,13 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
@@ -1118,7 +1118,7 @@
         <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.00571428571428</v>
+        <v>37.18571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1194,28 +1194,28 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.47</v>
+        <v>36.65</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1282,19 +1282,19 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>33</v>
-      </c>
       <c r="M10" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.05333333333333</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|10|11|25|33</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.72</v>
+        <v>35.9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>7|10|12|23|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M12" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.44727272727273</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|6|9|22|25</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -666,10 +666,10 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -763,10 +763,10 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.4</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
         <v>81</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.9</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.9</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.18571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1191,19 +1191,19 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
         <v>81</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
       <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" t="n">
-        <v>31</v>
-      </c>
       <c r="M11" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>36</v>
-      </c>
       <c r="M12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,16 +678,16 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -715,12 +715,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -803,12 +803,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -848,13 +848,13 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -891,12 +891,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -979,12 +979,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
         <v>25</v>
       </c>
-      <c r="L8" t="n">
-        <v>35</v>
-      </c>
       <c r="M8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>4|10|15|21|25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1191,19 +1191,19 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
         <v>81</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>27</v>
-      </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>5|6|10|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -678,16 +678,16 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.82</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.82</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
         <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>40.82</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>40.32</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>10|11|14|25|33</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>38.82</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -1112,13 +1112,13 @@
         <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.10571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|10|15|21|25</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>36.57</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1279,31 +1279,31 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.15333333333334</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|6|10|21|25</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1367,19 +1367,19 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
         <v>89</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.82</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>10|11|16|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.54727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.81999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -666,10 +666,10 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.82</v>
+        <v>47.86</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -763,10 +763,10 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.82</v>
+        <v>42.86</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -851,10 +851,10 @@
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.82</v>
+        <v>40.36</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>40.32</v>
+        <v>38.86</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10|11|14|25|33</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.82</v>
+        <v>38.86</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.10571428571428</v>
+        <v>37.86</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
         <v>9</v>
       </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.57</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1303,7 +1303,7 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.15333333333334</v>
+        <v>36.61</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>6|10|12|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J11" t="n">
-        <v>16</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.82</v>
+        <v>36.19333333333333</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>10|11|16|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>25</v>
@@ -1470,13 +1470,13 @@
         <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
       </c>
       <c r="P12" t="n">
         <v>23</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.54727272727273</v>
+        <v>35.58727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>4|6|12|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.86</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.86</v>
+        <v>47.96</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.86</v>
+        <v>42.96</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
-        <v>35</v>
-      </c>
       <c r="M5" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.36</v>
+        <v>40.46</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -939,10 +939,10 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.86</v>
+        <v>38.96</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>38.86</v>
+        <v>38.96</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.86</v>
+        <v>37.96</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1194,19 +1194,19 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.14571428571428</v>
+        <v>37.24571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1279,31 +1279,31 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.61</v>
+        <v>36.71</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|10|12|21|25</t>
+          <t>3|6|12|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1367,16 +1367,16 @@
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
         <v>27</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.19333333333333</v>
+        <v>36.29333333333334</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>27</v>
-      </c>
       <c r="M12" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.58727272727273</v>
+        <v>35.68727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|12|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.95999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.96</v>
+        <v>47.78</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.96</v>
+        <v>43.28</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -848,13 +848,13 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.46</v>
+        <v>42.78</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.96</v>
+        <v>38.78</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.96</v>
+        <v>37.78</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.96</v>
+        <v>37.06571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.24571428571429</v>
+        <v>36.53</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
@@ -1294,7 +1294,7 @@
         <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.71</v>
+        <v>36.11333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|6|12|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.29333333333334</v>
+        <v>35.78</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.68727272727273</v>
+        <v>35.50727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.78</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.78</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>43.28</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -848,13 +848,13 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>42.78</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.78</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.78</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.06571428571429</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.53</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.11333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.78</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.50727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.79</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>10|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>43.29</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -848,13 +848,13 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>42.79</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -939,7 +939,7 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
         <v>81</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>39.54</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
-        <v>13</v>
-      </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>38.79</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.79</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>37.07571428571428</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.12333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|33</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.79</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1455,13 +1455,13 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
         <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>23</v>
@@ -1470,7 +1470,7 @@
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.51727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>5|6|10|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.79</v>
+        <v>47.81</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>43.29</v>
+        <v>42.81</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
         <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>42.79</v>
+        <v>40.81</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
-        <v>36</v>
-      </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>39.54</v>
+        <v>40.31</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.79</v>
+        <v>38.81</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
         <v>25</v>
       </c>
-      <c r="L8" t="n">
-        <v>27</v>
-      </c>
       <c r="M8" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.79</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.07571428571428</v>
+        <v>36.56</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.12333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|10|15|23|33</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1367,31 +1367,31 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.79</v>
+        <v>35.81</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>4|6|12|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.51727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|6|10|23|25</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.81</v>
+        <v>73.92</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.81</v>
+        <v>47.92</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,7 +766,7 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.81</v>
+        <v>42.92</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.81</v>
+        <v>40.42</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>9|10|12|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>40.31</v>
+        <v>38.92</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.81</v>
+        <v>38.92</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.09571428571429</v>
+        <v>37.92</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.56</v>
+        <v>37.20571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.14333333333333</v>
+        <v>36.67</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1364,34 +1364,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" t="n">
-        <v>27</v>
-      </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.81</v>
+        <v>36.25333333333333</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|6|12|25|27</t>
+          <t>4|7|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
         <v>10</v>
       </c>
       <c r="K12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>31</v>
-      </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.53727272727272</v>
+        <v>35.64727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.92</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.92</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10|14|15|25|27</t>
+          <t>5|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -751,19 +751,19 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
         <v>85</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.92</v>
+        <v>45.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>3|10|12|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
@@ -854,7 +854,7 @@
         <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.42</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>9|10|12|25|35</t>
+          <t>9|10|14|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>38.92</v>
+        <v>39.59</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>6|10|11|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1015,13 +1015,13 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
@@ -1030,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.92</v>
+        <v>38.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>37.92</v>
+        <v>38.84</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
@@ -1206,7 +1206,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.20571428571429</v>
+        <v>37.84</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.67</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.25333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|7|10|21|25</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.64727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -766,16 +766,16 @@
         <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>45.84</v>
+        <v>45.85</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3|10|12|25|35</t>
+          <t>4|10|12|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>40.35</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>9|10|14|25|35</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>39.59</v>
+        <v>38.85</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|11|25|35</t>
+          <t>6|11|14|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.84</v>
+        <v>38.85</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
         <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>38.84</v>
+        <v>38.57727272727273</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
         <v>9</v>
       </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>16</v>
-      </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>37.12571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
+        <v>23</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" t="n">
-        <v>33</v>
-      </c>
       <c r="M11" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.17333333333333</v>
+        <v>36.6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>5|14|22|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.85</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -763,19 +763,19 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>45.85</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|10|12|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.35</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|11|14|25|35</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -1030,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.85</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>13</v>
-      </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>38.57727272727273</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.85</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>37.13571428571429</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.6</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
         <v>14</v>
       </c>
-      <c r="J12" t="n">
-        <v>22</v>
-      </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>27</v>
-      </c>
       <c r="M12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>36.18333333333334</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|14|22|25|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.96</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>3|10|12|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,7 +766,7 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.96</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>40.46</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>10|11|12|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>38.96</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -1027,10 +1027,10 @@
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>38.68727272727273</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>4|9|14|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M8" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.96</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>5|10|14|25|33</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>37.24571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.71</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>36.29333333333334</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1452,34 +1452,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.96</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.96</v>
+        <v>47.92</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.96</v>
+        <v>45.92</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.46</v>
+        <v>40.42</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10|11|12|25|35</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.96</v>
+        <v>38.92</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9</v>
-      </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.68727272727273</v>
+        <v>37.92</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|9|14|25|35</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.96</v>
+        <v>37.20571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1188,34 +1188,34 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
       <c r="M9" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.24571428571429</v>
+        <v>36.67</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
         <v>7</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
         <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.71</v>
+        <v>36.25333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>7|10|12|21|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
         <v>21</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.29333333333334</v>
+        <v>35.92</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>10|12|15|21|23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1452,34 +1452,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.96</v>
+        <v>35.64727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>4|6|11|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.92</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.92</v>
+        <v>47.93</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>45.92</v>
+        <v>42.93</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>9|10|15|25|36</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -845,16 +845,16 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>40.42</v>
+        <v>41.93</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.92</v>
+        <v>40.43</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>37.92</v>
+        <v>39.68</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>14</v>
@@ -1115,19 +1115,19 @@
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.20571428571429</v>
+        <v>37.93</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|14|25|33</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1188,31 +1188,31 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>21</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.67</v>
+        <v>37.21571428571428</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
         <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.25333333333333</v>
+        <v>36.26333333333334</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>7|10|12|21|27</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
         <v>10</v>
       </c>
-      <c r="I11" t="n">
-        <v>12</v>
-      </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.92</v>
+        <v>35.93</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>10|12|15|21|23</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M12" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.64727272727273</v>
+        <v>35.65727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|11|25|27</t>
+          <t>10|14|15|25|31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.93000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.93</v>
+        <v>47.77</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3|10|12|25|27</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -763,10 +763,10 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.93</v>
+        <v>42.77</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>9|10|15|25|36</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>41.93</v>
+        <v>41.77</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -927,31 +927,31 @@
         <v>3</v>
       </c>
       <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
         <v>6</v>
       </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.43</v>
+        <v>40.27</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
@@ -1030,7 +1030,7 @@
         <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.68</v>
+        <v>38.49727272727273</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>4|13|15|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
@@ -1118,16 +1118,16 @@
         <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.93</v>
+        <v>37.77</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1194,19 +1194,19 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>13</v>
-      </c>
       <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.21571428571428</v>
+        <v>37.05571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>27</v>
-      </c>
       <c r="M10" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.26333333333334</v>
+        <v>36.52</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1364,34 +1364,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.93</v>
+        <v>36.10333333333333</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
         <v>10</v>
-      </c>
-      <c r="H12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.65727272727273</v>
+        <v>35.77</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>10|14|15|25|31</t>
+          <t>5|9|10|25|30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.77</v>
+        <v>73.86</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.77</v>
+        <v>47.86</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.77</v>
+        <v>42.86</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>41.77</v>
+        <v>41.86</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.27</v>
+        <v>40.36</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M7" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>38.49727272727273</v>
+        <v>39.19333333333333</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|13|15|25|36</t>
+          <t>4|10|14|25|33</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>37.77</v>
+        <v>38.86</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1236,19 +1236,19 @@
         <v>0.5</v>
       </c>
       <c r="W9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>37.05571428571429</v>
+        <v>38.58727272727273</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1285,16 +1285,16 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.52</v>
+        <v>37.86</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>5|10|12|21|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1391,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.10333333333333</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>6|10|12|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>30</v>
-      </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.77</v>
+        <v>36.61</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|9|10|25|30</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.86</v>
+        <v>73.87</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.86</v>
+        <v>47.87</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.86</v>
+        <v>42.87</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>41.86</v>
+        <v>41.87</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -930,28 +930,28 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
-        <v>27</v>
-      </c>
       <c r="M6" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.36</v>
+        <v>40.37</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>4|7|10|21|25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.19333333333333</v>
+        <v>39.20333333333333</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1103,13 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>38.86</v>
+        <v>38.87</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>1|10|15|25|36</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1236,19 +1236,19 @@
         <v>0.5</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>38.58727272727273</v>
+        <v>37.87</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>37.86</v>
+        <v>37.15571428571428</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1364,34 +1364,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>37.14571428571428</v>
+        <v>36.62</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|10|12|21|25</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M12" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>36.61</v>
+        <v>35.59727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>10|14|15|25|31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.87</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.87</v>
+        <v>47.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>4|5|10|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -751,31 +751,31 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.87</v>
+        <v>42.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|10|14|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
         <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>41.87</v>
+        <v>40.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -927,22 +927,22 @@
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.37</v>
+        <v>40.4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|21|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.20333333333333</v>
+        <v>40.18571428571428</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|10|14|25|33</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1100,34 +1100,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>38.87</v>
+        <v>38.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1|10|15|25|36</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.87</v>
+        <v>36.65</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>37.15571428571428</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|10|12|21|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>7</v>
       </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.62</v>
+        <v>35.9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>7|9|14|24|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
         <v>10</v>
-      </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M12" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.59727272727272</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>10|14|15|25|31</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4|5|10|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -751,31 +751,31 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|10|14|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -836,22 +836,22 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
         <v>77</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.9</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.4</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>40.18571428571428</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1100,34 +1100,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>38.9</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>7|9|14|24|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1458,19 +1458,19 @@
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>36</v>
-      </c>
       <c r="M12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,31 +575,31 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
         <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.8</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>5|7|10|34|36</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>9|10|12|25|35</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,7 +766,7 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -836,34 +836,34 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35</v>
+      </c>
+      <c r="M5" t="n">
+        <v>80</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L5" t="n">
-        <v>27</v>
-      </c>
-      <c r="M5" t="n">
-        <v>77</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>41.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
-        <v>35</v>
-      </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>40.3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -1027,7 +1027,7 @@
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
         <v>85</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>39.13333333333333</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>4|7|14|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1188,31 +1188,31 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>21</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>37.08571428571428</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>27</v>
-      </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.55</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>7|9|10|24|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|27|35</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1455,13 +1455,13 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>23</v>
@@ -1470,7 +1470,7 @@
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.52727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>8|10|15|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,22 +575,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.8</v>
+        <v>73.97</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>5|7|10|34|36</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.8</v>
+        <v>47.97</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>9|10|12|25|35</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -748,34 +748,34 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>14</v>
-      </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.8</v>
+        <v>43.47</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -836,34 +836,34 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>41.8</v>
+        <v>42.97</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -936,13 +936,13 @@
         <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>40.3</v>
+        <v>41.97</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.13333333333333</v>
+        <v>39.30333333333333</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|7|14|25|35</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1103,19 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
         <v>75</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.8</v>
+        <v>37.97</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>5|10|12|21|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1194,28 +1194,28 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.08571428571428</v>
+        <v>37.25571428571428</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
         <v>7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.55</v>
+        <v>36.72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>7|9|10|24|25</t>
+          <t>6|7|10|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.8</v>
+        <v>35.97</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|14|27|35</t>
+          <t>4|6|7|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
         <v>10</v>
       </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.52727272727273</v>
+        <v>35.69727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>8|10|15|23|25</t>
+          <t>1|9|10|22|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.97</v>
+        <v>73.88</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
         <v>14</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.97</v>
+        <v>47.88</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>10|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -754,28 +754,28 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>43.47</v>
+        <v>43.38</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>4|10|15|25|33</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -839,13 +839,13 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
@@ -854,16 +854,16 @@
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>42.97</v>
+        <v>42.88</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -927,13 +927,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>41.97</v>
+        <v>41.88</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>4|11|14|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.30333333333333</v>
+        <v>40.88</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1100,34 +1100,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>37.97</v>
+        <v>39.21333333333333</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|12|21|27</t>
+          <t>4|8|10|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.25571428571428</v>
+        <v>37.16571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1279,13 +1279,13 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
@@ -1294,7 +1294,7 @@
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.72</v>
+        <v>36.63</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6|7|10|23|25</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1370,28 +1370,28 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.97</v>
+        <v>35.88</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|6|7|21|25</t>
+          <t>4|10|14|25|31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -1464,13 +1464,13 @@
         <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.69727272727273</v>
+        <v>35.60727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1|9|10|22|25</t>
+          <t>7|9|10|24|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.88</v>
+        <v>73.95</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.88</v>
+        <v>47.95</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10|14|15|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>43.38</v>
+        <v>43.45</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|10|15|25|33</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -839,31 +839,31 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
+        <v>33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
         <v>27</v>
-      </c>
-      <c r="M5" t="n">
-        <v>76</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>42.88</v>
+        <v>42.95</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -927,13 +927,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
@@ -942,7 +942,7 @@
         <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>41.88</v>
+        <v>41.95</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|11|14|25|35</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
@@ -1030,16 +1030,16 @@
         <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>40.88</v>
+        <v>39.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>4|8|10|25|35</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1100,34 +1100,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
       <c r="P8" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>39.21333333333333</v>
+        <v>37.95</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4|8|10|25|35</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>6</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.16571428571429</v>
+        <v>37.23571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.63</v>
+        <v>36.28333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1367,31 +1367,31 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.88</v>
+        <v>35.95</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|10|14|25|31</t>
+          <t>1|6|10|21|29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.60727272727273</v>
+        <v>35.67727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.95</v>
+        <v>73.78</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -663,31 +663,31 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -708,19 +708,19 @@
         <v>0.5</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>47.95</v>
+        <v>50.78</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|10|14|25|35</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
         <v>77</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>43.45</v>
+        <v>42.78</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>6|9|10|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>42.95</v>
+        <v>40.28</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>10|12|13|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>41.95</v>
+        <v>39.53</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>39.7</v>
+        <v>38.78</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|8|10|25|35</t>
+          <t>4|13|15|25|36</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>22</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>25</v>
       </c>
-      <c r="L8" t="n">
-        <v>27</v>
-      </c>
       <c r="M8" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.95</v>
+        <v>38.78</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
         <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.23571428571429</v>
+        <v>37.78</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.28333333333333</v>
+        <v>37.06571428571429</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>4|5|10|19|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.95</v>
+        <v>36.11333333333333</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1|6|10|21|29</t>
+          <t>5|7|10|25|32</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.67727272727272</v>
+        <v>35.50727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|9|10|24|25</t>
+          <t>6|10|11|21|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.78</v>
+        <v>73.98</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -663,31 +663,31 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
       <c r="K3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" t="n">
         <v>25</v>
       </c>
-      <c r="L3" t="n">
-        <v>35</v>
-      </c>
       <c r="M3" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -708,19 +708,19 @@
         <v>0.5</v>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>50.78</v>
+        <v>47.98</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4|10|14|25|35</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
         <v>77</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.78</v>
+        <v>43.48</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6|9|10|25|27</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.28</v>
+        <v>42.98</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10|12|13|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>39.53</v>
+        <v>38.98</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
+        <v>23</v>
+      </c>
+      <c r="L7" t="n">
         <v>25</v>
       </c>
-      <c r="L7" t="n">
-        <v>36</v>
-      </c>
       <c r="M7" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0.5</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.78</v>
+        <v>37.98</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|13|15|25|36</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>38.78</v>
+        <v>37.26571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>2|7|12|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
@@ -1206,7 +1206,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.78</v>
+        <v>36.73</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>37.06571428571429</v>
+        <v>36.31333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|5|10|19|25</t>
+          <t>10|12|17|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.11333333333333</v>
+        <v>35.98</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|7|10|25|32</t>
+          <t>5|6|10|23|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
         <v>10</v>
       </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.50727272727273</v>
+        <v>35.70727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|7|10|25|32</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,22 +575,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
       <c r="K2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.98</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>5|7|10|34|36</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.98</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>43.48</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>10|11|14|25|35</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
         <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>42.98</v>
+        <v>40.84</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -933,16 +933,16 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.98</v>
+        <v>40.34</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
       <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>25</v>
       </c>
       <c r="M7" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.98</v>
+        <v>38.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1103,22 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.26571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|7|12|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.73</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1279,31 +1279,31 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="n">
-        <v>12</v>
-      </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>27</v>
-      </c>
       <c r="M10" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.31333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>10|12|17|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
         <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
         <v>71</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.98</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|6|10|23|27</t>
+          <t>6|7|10|23|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
       <c r="P12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.70727272727272</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|7|10|25|32</t>
+          <t>2|7|12|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.91</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.91</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -751,10 +751,10 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
@@ -763,10 +763,10 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.91</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>10|11|14|25|35</t>
+          <t>7|10|14|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -851,10 +851,10 @@
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.84</v>
+        <v>40.41</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|9|10|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -924,25 +924,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>40.34</v>
+        <v>40.19571428571428</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.84</v>
+        <v>38.91</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
       <c r="K8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L8" t="n">
         <v>25</v>
       </c>
-      <c r="L8" t="n">
-        <v>31</v>
-      </c>
       <c r="M8" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.91</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -1206,16 +1206,16 @@
         <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>36.66</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>9|10|12|21|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -1288,22 +1288,22 @@
         <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
       <c r="P10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.24333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
         <v>6</v>
       </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.91</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|7|10|23|25</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1455,31 +1455,31 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>68</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M12" t="n">
-        <v>73</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.63727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2|7|12|25|27</t>
+          <t>4|6|10|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.91</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.91</v>
+        <v>47.85</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4|14|15|25|27</t>
+          <t>7|10|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,7 +766,7 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.91</v>
+        <v>42.85</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>7|10|14|25|27</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -854,7 +854,7 @@
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.41</v>
+        <v>40.35</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4|9|10|25|27</t>
+          <t>6|9|10|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -942,7 +942,7 @@
         <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>40.19571428571428</v>
+        <v>39.18333333333334</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1015,22 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
       <c r="K7" t="n">
+        <v>22</v>
+      </c>
+      <c r="L7" t="n">
         <v>25</v>
       </c>
-      <c r="L7" t="n">
-        <v>27</v>
-      </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.91</v>
+        <v>38.85</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1106,19 +1106,19 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.91</v>
+        <v>37.85</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.66</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -1291,19 +1291,19 @@
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.24333333333333</v>
+        <v>36.6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>4|10|14|25|29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.91</v>
+        <v>35.85</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1461,25 +1461,25 @@
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
         <v>23</v>
-      </c>
-      <c r="L12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>68</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.63727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|10|23|25</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,31 +575,31 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>10</v>
       </c>
       <c r="K2" t="n">
+        <v>33</v>
+      </c>
+      <c r="L2" t="n">
+        <v>35</v>
+      </c>
+      <c r="M2" t="n">
+        <v>85</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
         <v>34</v>
-      </c>
-      <c r="L2" t="n">
-        <v>36</v>
-      </c>
-      <c r="M2" t="n">
-        <v>92</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>31</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>5|7|10|34|36</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
         <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.85</v>
+        <v>47.89</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|10|14|25|27</t>
+          <t>4|5|10|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,16 +766,16 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.85</v>
+        <v>42.89</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|14|15|25|27</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -848,13 +848,13 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
-        <v>27</v>
-      </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.35</v>
+        <v>40.39</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6|9|10|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -942,7 +942,7 @@
         <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>39.18333333333334</v>
+        <v>40.17571428571429</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1015,31 +1015,31 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.85</v>
+        <v>38.89</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1106,16 +1106,16 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
         <v>85</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.85</v>
+        <v>37.89</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>5|12|16|25|27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
         <v>21</v>
@@ -1206,13 +1206,13 @@
         <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>21</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.13571428571429</v>
+        <v>36.64</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>4|10|15|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>29</v>
-      </c>
       <c r="M10" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.6</v>
+        <v>36.22333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4|10|14|25|29</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1367,31 +1367,31 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
+        <v>36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>82</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
         <v>31</v>
-      </c>
-      <c r="M11" t="n">
-        <v>89</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.85</v>
+        <v>35.89</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|10|25|36</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
         <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.61727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>5|11|14|22|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.89</v>
+        <v>73.84</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.89</v>
+        <v>47.84</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4|5|10|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -766,16 +766,16 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.89</v>
+        <v>42.84</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -842,19 +842,19 @@
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.39</v>
+        <v>40.34</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -939,7 +939,7 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
         <v>81</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.17571428571429</v>
+        <v>38.84</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -1030,16 +1030,16 @@
         <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.89</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5|12|16|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -1200,13 +1200,13 @@
         <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4|10|15|21|25</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.22333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>9|10|12|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1367,31 +1367,31 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" t="n">
-        <v>36</v>
-      </c>
       <c r="M11" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.89</v>
+        <v>35.84</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>5|6|10|25|36</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1455,19 +1455,19 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M12" t="n">
         <v>79</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.61727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>5|11|14|22|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84</v>
+        <v>73.87</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.84</v>
+        <v>47.87</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>12|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -775,7 +775,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.84</v>
+        <v>42.87</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>4|9|10|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.34</v>
+        <v>40.37</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>10|12|13|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -927,31 +927,31 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>38.84</v>
+        <v>38.87</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>8|10|14|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1015,13 +1015,13 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.84</v>
+        <v>37.87</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>5|12|16|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.15571428571428</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>6|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.59</v>
+        <v>36.62</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1279,10 +1279,10 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1291,10 +1291,10 @@
         <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.20333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>7|9|10|25|32</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1367,13 +1367,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
         <v>21</v>
@@ -1382,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.84</v>
+        <v>35.87</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.59727272727272</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>33</v>
@@ -590,16 +590,16 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.87</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>14</v>
@@ -678,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>47.87</v>
+        <v>47.85</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>12|14|15|25|27</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,16 +766,16 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.87</v>
+        <v>42.85</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4|9|10|25|27</t>
+          <t>8|10|14|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -839,13 +839,13 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
@@ -854,7 +854,7 @@
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.37</v>
+        <v>40.35</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10|12|13|25|27</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -924,34 +924,34 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>38.87</v>
+        <v>40.13571428571429</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8|10|14|25|27</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1012,22 +1012,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
         <v>85</v>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>37.87</v>
+        <v>38.85</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|12|16|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M8" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>37.15571428571428</v>
+        <v>38.57727272727273</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6|10|11|25|35</t>
+          <t>3|8|10|25|33</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>36.62</v>
+        <v>37.85</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1276,25 +1276,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
-        <v>32</v>
-      </c>
       <c r="M10" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1303,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.20333333333333</v>
+        <v>36.6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>7|9|10|25|32</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1364,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>35.87</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>9|10|12|21|25</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="H12" t="n">
-        <v>7</v>
-      </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.59727272727272</v>
+        <v>35.85</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>10|12|17|25|27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/daily_lotto_ensemble_predictions.xlsx
@@ -575,22 +575,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
       <c r="K2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>5|7|10|34|36</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -666,28 +666,28 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -708,19 +708,19 @@
         <v>0.5</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>47.85</v>
+        <v>50.89</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4|14|15|25|27</t>
+          <t>4|10|14|25|35</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
@@ -766,16 +766,16 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -799,16 +799,16 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>42.85</v>
+        <v>42.89</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>8|10|14|25|27</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -839,13 +839,13 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
@@ -854,7 +854,7 @@
         <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -887,16 +887,16 @@
         <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>40.35</v>
+        <v>40.39</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>5|6|12|25|27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -939,10 +939,10 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>40.13571428571429</v>
+        <v>38.89</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>4|9|10|25|27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -1027,19 +1027,19 @@
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>38.85</v>
+        <v>37.89</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>8|10|14|25|27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
         <v>0.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>38.57727272727273</v>
+        <v>37.17571428571429</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3|8|10|25|33</t>
+          <t>6|10|11|25|35</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
       </c>
       <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
       <c r="M9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>37.85</v>
+        <v>36.64</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>6|7|10|21|25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>36.6</v>
+        <v>36.22333333333333</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1415,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>36.18333333333334</v>
+        <v>35.89</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
         <v>25</v>
       </c>
-      <c r="L12" t="n">
-        <v>27</v>
-      </c>
       <c r="M12" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>35.85</v>
+        <v>35.61727272727273</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>10|12|17|25|27</t>
+          <t>4|10|13|23|25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
